--- a/output/pdf_financials_xlsx/CEI.xlsx
+++ b/output/pdf_financials_xlsx/CEI.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11.163</v>
+        <v>-11.163</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-6.573</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>11.163</v>
+        <v>-11.163</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-6.573</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>11.163</v>
+        <v>-11.163</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-6.573</v>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-260.8</v>
+        <v>260.8</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-372.1</v>
+        <v>372.1</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.479</v>
+        <v>-9.847</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.657</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.479</v>
+        <v>-9.847</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.657</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>137.0707778556412</v>
+        <v>-137.0707778556412</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>217.177166724678</v>
+        <v>-171.3713887922032</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-70.6803247004252</v>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>137.0707778556412</v>
+        <v>-137.0707778556412</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>194.2742777584407</v>
+        <v>-194.2742777584407</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>-127.0390413606494</v>
@@ -9486,13 +9486,13 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>7.824</v>
+        <v>-7.824</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>11.163</v>
+        <v>-11.163</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>6.573</v>
+        <v>-6.573</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CEI.xlsx
+++ b/output/pdf_financials_xlsx/CEI.xlsx
@@ -1166,10 +1166,10 @@
         <v>65.41</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>82.568</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.693</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -1210,10 +1210,10 @@
         <v>65.41</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>82.568</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.693</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         <v>1.041</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>83.477</v>
+        <v>0.909</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.849</v>
+        <v>1.156</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.474</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEI.xlsx
+++ b/output/pdf_financials_xlsx/CEI.xlsx
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2004,16 +2004,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>38.101</v>
+        <v>38.211</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>19.767</v>
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.402</v>
+        <v>1.312</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.378</v>
+        <v>1.943</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
@@ -2201,23 +2201,17 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.0004349987571464081</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.000927099106894527</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.002521461404251126</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.2267525248617798</v>
+        <v>0.2274071737616721</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>0.1219417403856831</v>
@@ -4399,7 +4393,11 @@
           <t>Current portion of lease obligations (7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -4637,7 +4635,11 @@
           <t>Current portion of lease obligations (8)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.007</v>
       </c>
@@ -6425,7 +6427,11 @@
           <t>Deferred income tax recovery (16)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
